--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103996148</v>
+        <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>81456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550237</v>
+        <v>550276</v>
       </c>
       <c r="R4" t="n">
-        <v>6994140</v>
+        <v>6994130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,11 +973,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -997,23 +982,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996148</t>
+          <t>https://artportalen.se/Sighting/136617320</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121002233</v>
+        <v>103996148</v>
       </c>
       <c r="B5" t="n">
         <v>91909</v>
@@ -1042,22 +1023,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550145</v>
+        <v>550237</v>
       </c>
       <c r="R5" t="n">
-        <v>6994163</v>
+        <v>6994140</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1059,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,9 +1083,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1107,19 +1099,23 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002233</t>
+          <t>https://artportalen.se/Sighting/103996148</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121002784</v>
+        <v>121002233</v>
       </c>
       <c r="B6" t="n">
         <v>91909</v>
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550165</v>
+        <v>550145</v>
       </c>
       <c r="R6" t="n">
-        <v>6994154</v>
+        <v>6994163</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,13 +1215,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002784</t>
+          <t>https://artportalen.se/Sighting/121002233</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004243</v>
+        <v>121002784</v>
       </c>
       <c r="B7" t="n">
         <v>91909</v>
@@ -1263,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550240</v>
+        <v>550165</v>
       </c>
       <c r="R7" t="n">
-        <v>6994134</v>
+        <v>6994154</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,54 +1321,57 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004243</t>
+          <t>https://artportalen.se/Sighting/121002784</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103996059</v>
+        <v>121004243</v>
       </c>
       <c r="B8" t="n">
-        <v>96338</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550310</v>
+        <v>550240</v>
       </c>
       <c r="R8" t="n">
-        <v>6994183</v>
+        <v>6994134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1395,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,13 +1409,9 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1436,61 +1421,57 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/121004243</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134246391</v>
+        <v>103996059</v>
       </c>
       <c r="B9" t="n">
-        <v>93271</v>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550317</v>
+        <v>550310</v>
       </c>
       <c r="R9" t="n">
-        <v>6994117</v>
+        <v>6994183</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,12 +1498,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,72 +1524,78 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121003233</v>
+        <v>134246391</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550151</v>
+        <v>550317</v>
       </c>
       <c r="R10" t="n">
-        <v>6994084</v>
+        <v>6994117</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,12 +1619,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,56 +1633,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003233</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121001372</v>
+        <v>121003233</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550123</v>
+        <v>550151</v>
       </c>
       <c r="R11" t="n">
-        <v>6994147</v>
+        <v>6994084</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1760,13 +1756,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121001372</t>
+          <t>https://artportalen.se/Sighting/121003233</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121001617</v>
+        <v>121001372</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1804,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550137</v>
+        <v>550123</v>
       </c>
       <c r="R12" t="n">
-        <v>6994152</v>
+        <v>6994147</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1866,13 +1862,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121001617</t>
+          <t>https://artportalen.se/Sighting/121001372</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121002081</v>
+        <v>121001617</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1910,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550141</v>
+        <v>550137</v>
       </c>
       <c r="R13" t="n">
-        <v>6994157</v>
+        <v>6994152</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,11 +1944,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1977,13 +1968,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002081</t>
+          <t>https://artportalen.se/Sighting/121001617</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121002900</v>
+        <v>121002081</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2021,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550164</v>
+        <v>550141</v>
       </c>
       <c r="R14" t="n">
-        <v>6994129</v>
+        <v>6994157</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2059,6 +2050,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2083,13 +2079,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002900</t>
+          <t>https://artportalen.se/Sighting/121002081</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121002972</v>
+        <v>121002900</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550152</v>
+        <v>550164</v>
       </c>
       <c r="R15" t="n">
-        <v>6994109</v>
+        <v>6994129</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2165,11 +2161,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2194,13 +2185,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002972</t>
+          <t>https://artportalen.se/Sighting/121002900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004337</v>
+        <v>121002972</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2238,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550319</v>
+        <v>550152</v>
       </c>
       <c r="R16" t="n">
-        <v>6994143</v>
+        <v>6994109</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2278,7 +2269,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,16 +2296,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121002972</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134246395</v>
+        <v>121004337</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,19 +2331,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550292</v>
+        <v>550319</v>
       </c>
       <c r="R17" t="n">
-        <v>6994150</v>
+        <v>6994143</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,12 +2370,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,74 +2389,72 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121001781</v>
+        <v>134246395</v>
       </c>
       <c r="B18" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550136</v>
+        <v>550292</v>
       </c>
       <c r="R18" t="n">
-        <v>6994142</v>
+        <v>6994150</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,17 +2478,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,31 +2492,30 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121001781</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121003046</v>
+        <v>121001781</v>
       </c>
       <c r="B19" t="n">
         <v>80432</v>
@@ -2562,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550156</v>
+        <v>550136</v>
       </c>
       <c r="R19" t="n">
-        <v>6994109</v>
+        <v>6994142</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2629,13 +2620,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003046</t>
+          <t>https://artportalen.se/Sighting/121001781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121003623</v>
+        <v>121003046</v>
       </c>
       <c r="B20" t="n">
         <v>80432</v>
@@ -2673,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550173</v>
+        <v>550156</v>
       </c>
       <c r="R20" t="n">
-        <v>6994058</v>
+        <v>6994109</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2740,13 +2731,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003623</t>
+          <t>https://artportalen.se/Sighting/121003046</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121003793</v>
+        <v>121003623</v>
       </c>
       <c r="B21" t="n">
         <v>80432</v>
@@ -2784,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550193</v>
+        <v>550173</v>
       </c>
       <c r="R21" t="n">
-        <v>6994068</v>
+        <v>6994058</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2824,7 +2815,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,13 +2842,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003793</t>
+          <t>https://artportalen.se/Sighting/121003623</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121003973</v>
+        <v>121003793</v>
       </c>
       <c r="B22" t="n">
         <v>80432</v>
@@ -2895,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550184</v>
+        <v>550193</v>
       </c>
       <c r="R22" t="n">
-        <v>6994074</v>
+        <v>6994068</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2933,6 +2924,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2957,16 +2953,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003973</t>
+          <t>https://artportalen.se/Sighting/121003793</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134246401</v>
+        <v>121003973</v>
       </c>
       <c r="B23" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,19 +2988,22 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550158</v>
+        <v>550184</v>
       </c>
       <c r="R23" t="n">
-        <v>6994115</v>
+        <v>6994074</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3028,12 +3027,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,74 +3041,72 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246401</t>
+          <t>https://artportalen.se/Sighting/121003973</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121001866</v>
+        <v>134246401</v>
       </c>
       <c r="B24" t="n">
-        <v>80461</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550136</v>
+        <v>550158</v>
       </c>
       <c r="R24" t="n">
-        <v>6994142</v>
+        <v>6994115</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3133,17 +3130,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På asp tillsammans med lunglav</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,31 +3144,30 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121001866</t>
+          <t>https://artportalen.se/Sighting/134246401</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121003862</v>
+        <v>121001866</v>
       </c>
       <c r="B25" t="n">
         <v>80461</v>
@@ -3214,10 +3205,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550193</v>
+        <v>550136</v>
       </c>
       <c r="R25" t="n">
-        <v>6994068</v>
+        <v>6994142</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3254,7 +3245,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,16 +3272,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003862</t>
+          <t>https://artportalen.se/Sighting/121001866</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134246399</v>
+        <v>121003862</v>
       </c>
       <c r="B26" t="n">
-        <v>80493</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,19 +3307,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550158</v>
+        <v>550193</v>
       </c>
       <c r="R26" t="n">
-        <v>6994115</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3352,12 +3346,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,33 +3365,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246399</t>
+          <t>https://artportalen.se/Sighting/121003862</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121003824</v>
+        <v>134246399</v>
       </c>
       <c r="B27" t="n">
-        <v>80467</v>
+        <v>80493</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,40 +3400,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550193</v>
+        <v>550158</v>
       </c>
       <c r="R27" t="n">
-        <v>6994068</v>
+        <v>6994115</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3457,17 +3454,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,34 +3468,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003824</t>
+          <t>https://artportalen.se/Sighting/134246399</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121003077</v>
+        <v>121003824</v>
       </c>
       <c r="B28" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550156</v>
+        <v>550193</v>
       </c>
       <c r="R28" t="n">
-        <v>6994109</v>
+        <v>6994068</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3578,7 +3569,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3605,16 +3596,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003077</t>
+          <t>https://artportalen.se/Sighting/121003824</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121001246</v>
+        <v>121003077</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3622,31 +3613,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3654,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550118</v>
+        <v>550156</v>
       </c>
       <c r="R29" t="n">
-        <v>6994138</v>
+        <v>6994109</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3694,15 +3680,16 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kraftigt bearbetad grov låga, troligen av spillkråka.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3720,16 +3707,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121001246</t>
+          <t>https://artportalen.se/Sighting/121003077</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246404</v>
+        <v>121001246</v>
       </c>
       <c r="B30" t="n">
-        <v>58461</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,21 +3724,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3759,23 +3746,23 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550235</v>
+        <v>550118</v>
       </c>
       <c r="R30" t="n">
-        <v>6994071</v>
+        <v>6994138</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3799,19 +3786,24 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kraftigt bearbetad grov låga, troligen av spillkråka.</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -3819,69 +3811,73 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246404</t>
+          <t>https://artportalen.se/Sighting/121001246</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121002529</v>
+        <v>134246404</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>58461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550155</v>
+        <v>550235</v>
       </c>
       <c r="R31" t="n">
-        <v>6994168</v>
+        <v>6994071</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3905,17 +3901,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rik förekomst inom ca 1 x 1 meter.</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3924,31 +3915,30 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002529</t>
+          <t>https://artportalen.se/Sighting/134246404</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121002758</v>
+        <v>121002529</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3987,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550165</v>
+        <v>550155</v>
       </c>
       <c r="R32" t="n">
-        <v>6994154</v>
+        <v>6994168</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4025,6 +4015,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rik förekomst inom ca 1 x 1 meter.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4049,13 +4044,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121002758</t>
+          <t>https://artportalen.se/Sighting/121002529</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121003368</v>
+        <v>121002758</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4094,10 +4089,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550164</v>
+        <v>550165</v>
       </c>
       <c r="R33" t="n">
-        <v>6994073</v>
+        <v>6994154</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4156,13 +4151,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003368</t>
+          <t>https://artportalen.se/Sighting/121002758</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121003525</v>
+        <v>121003368</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550173</v>
+        <v>550164</v>
       </c>
       <c r="R34" t="n">
-        <v>6994064</v>
+        <v>6994073</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4263,13 +4258,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003525</t>
+          <t>https://artportalen.se/Sighting/121003368</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004113</v>
+        <v>121003525</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4308,10 +4303,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550183</v>
+        <v>550173</v>
       </c>
       <c r="R35" t="n">
-        <v>6994078</v>
+        <v>6994064</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4370,13 +4365,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004113</t>
+          <t>https://artportalen.se/Sighting/121003525</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004238</v>
+        <v>121004113</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4415,10 +4410,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550211</v>
+        <v>550183</v>
       </c>
       <c r="R36" t="n">
-        <v>6994140</v>
+        <v>6994078</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4477,13 +4472,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004238</t>
+          <t>https://artportalen.se/Sighting/121004113</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004332</v>
+        <v>121004238</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4522,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550310</v>
+        <v>550211</v>
       </c>
       <c r="R37" t="n">
-        <v>6994126</v>
+        <v>6994140</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4584,54 +4579,58 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/121004238</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134246406</v>
+        <v>121004332</v>
       </c>
       <c r="B38" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550277</v>
+        <v>550310</v>
       </c>
       <c r="R38" t="n">
-        <v>6994166</v>
+        <v>6994126</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4655,12 +4654,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,74 +4668,77 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121003107</v>
+        <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>80392</v>
+        <v>99342</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550156</v>
+        <v>550221</v>
       </c>
       <c r="R39" t="n">
-        <v>6994109</v>
+        <v>6994147</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4760,17 +4762,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4779,7 +4776,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4797,51 +4793,56 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121003107</t>
+          <t>https://artportalen.se/Sighting/136617174</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134246400</v>
+        <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>99342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550158</v>
+        <v>550248</v>
       </c>
       <c r="R40" t="n">
-        <v>6994115</v>
+        <v>6994153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4868,12 +4869,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4888,16 +4889,331 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136617265</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121003107</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>550156</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6994109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003107</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134246400</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6994115</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134246400</t>
         </is>
@@ -4944,6 +5260,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81456</v>
+        <v>81458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136617320</v>
       </c>
       <c r="B4" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4721,11 +4721,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
@@ -4828,11 +4824,7 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -4695,7 +4695,7 @@
         <v>136617174</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136617265</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
